--- a/Team-Data/2012-13/3-8-2012-13.xlsx
+++ b/Team-Data/2012-13/3-8-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I2" t="n">
         <v>37.5</v>
       </c>
       <c r="J2" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.463</v>
@@ -691,7 +758,7 @@
         <v>23.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
         <v>13.6</v>
@@ -700,19 +767,19 @@
         <v>19.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="R2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T2" t="n">
         <v>40.6</v>
       </c>
       <c r="U2" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V2" t="n">
         <v>15</v>
@@ -721,37 +788,37 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AD2" t="n">
         <v>20</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG2" t="n">
         <v>10</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>6</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -790,7 +857,7 @@
         <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
         <v>17</v>
@@ -811,7 +878,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L3" t="n">
         <v>5.9</v>
@@ -873,7 +940,7 @@
         <v>16.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="O3" t="n">
         <v>16.2</v>
@@ -882,16 +949,16 @@
         <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S3" t="n">
         <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U3" t="n">
         <v>23.2</v>
@@ -912,10 +979,10 @@
         <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>0.4</v>
@@ -924,19 +991,19 @@
         <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -957,16 +1024,16 @@
         <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>28</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.581</v>
+        <v>0.574</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O4" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P4" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.735</v>
+        <v>0.738</v>
       </c>
       <c r="R4" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S4" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
         <v>15</v>
@@ -1085,25 +1152,25 @@
         <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z4" t="n">
         <v>18.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
         <v>95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,40 +1200,40 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>3</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>0.21</v>
+        <v>0.213</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1231,13 +1298,13 @@
         <v>0.418</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O5" t="n">
         <v>18.9</v>
@@ -1246,25 +1313,25 @@
         <v>25.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R5" t="n">
         <v>11.4</v>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T5" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U5" t="n">
         <v>19</v>
       </c>
       <c r="V5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
         <v>6.1</v>
@@ -1273,7 +1340,7 @@
         <v>7.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA5" t="n">
         <v>21.5</v>
@@ -1282,10 +1349,10 @@
         <v>93</v>
       </c>
       <c r="AC5" t="n">
-        <v>-10.5</v>
+        <v>-10.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1312,7 +1379,7 @@
         <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
         <v>27</v>
@@ -1321,16 +1388,16 @@
         <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
         <v>27</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" t="n">
         <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J6" t="n">
         <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L6" t="n">
         <v>4.9</v>
@@ -1419,28 +1486,28 @@
         <v>14.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O6" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P6" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S6" t="n">
         <v>30.7</v>
       </c>
       <c r="T6" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="U6" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
         <v>14.7</v>
@@ -1449,16 +1516,16 @@
         <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z6" t="n">
         <v>19.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB6" t="n">
         <v>92.5</v>
@@ -1467,16 +1534,16 @@
         <v>1.1</v>
       </c>
       <c r="AD6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE6" t="n">
         <v>11</v>
       </c>
-      <c r="AE6" t="n">
-        <v>10</v>
-      </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1488,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1497,34 +1564,34 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ6" t="n">
         <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>16</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1536,7 +1603,7 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -1571,34 +1638,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84</v>
+        <v>84.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
         <v>0.354</v>
@@ -1607,19 +1674,19 @@
         <v>17.5</v>
       </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q7" t="n">
         <v>0.764</v>
       </c>
       <c r="R7" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
         <v>28.2</v>
       </c>
       <c r="T7" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
@@ -1628,7 +1695,7 @@
         <v>14.1</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X7" t="n">
         <v>3.9</v>
@@ -1637,61 +1704,61 @@
         <v>7.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
         <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1700,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
         <v>6</v>
@@ -1709,7 +1776,7 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY7" t="n">
         <v>29</v>
@@ -1718,13 +1785,13 @@
         <v>24</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" t="n">
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.459</v>
+        <v>0.45</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
@@ -1771,40 +1838,40 @@
         <v>38.4</v>
       </c>
       <c r="J8" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L8" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T8" t="n">
         <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V8" t="n">
         <v>14.3</v>
@@ -1813,13 +1880,13 @@
         <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y8" t="n">
         <v>4.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA8" t="n">
         <v>19.4</v>
@@ -1828,7 +1895,7 @@
         <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AD8" t="n">
         <v>20</v>
@@ -1849,25 +1916,25 @@
         <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK8" t="n">
         <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,28 +1943,28 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -2037,7 +2104,7 @@
         <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
         <v>18</v>
@@ -2055,7 +2122,7 @@
         <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
         <v>11</v>
@@ -2064,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2088,7 +2155,7 @@
         <v>3</v>
       </c>
       <c r="BC9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -2117,70 +2184,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0.359</v>
+        <v>0.365</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J10" t="n">
-        <v>81.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="O10" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P10" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="R10" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T10" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U10" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W10" t="n">
         <v>6.9</v>
       </c>
       <c r="X10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z10" t="n">
         <v>19.7</v>
@@ -2189,13 +2256,13 @@
         <v>20.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC10" t="n">
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,7 +2271,7 @@
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -2225,13 +2292,13 @@
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>28</v>
@@ -2249,7 +2316,7 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
         <v>26</v>
@@ -2267,7 +2334,7 @@
         <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
         <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0.556</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,10 +2384,10 @@
         <v>37.8</v>
       </c>
       <c r="J11" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
@@ -2329,28 +2396,28 @@
         <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.395</v>
+        <v>0.394</v>
       </c>
       <c r="O11" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P11" t="n">
         <v>21.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.798</v>
+        <v>0.8</v>
       </c>
       <c r="R11" t="n">
         <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V11" t="n">
         <v>15.3</v>
@@ -2365,28 +2432,28 @@
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA11" t="n">
         <v>19.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC11" t="n">
         <v>-0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>18</v>
@@ -2419,7 +2486,7 @@
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2428,13 +2495,13 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW11" t="n">
         <v>27</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>28</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>0.54</v>
+        <v>0.532</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="J12" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L12" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O12" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0.753</v>
       </c>
       <c r="R12" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U12" t="n">
         <v>23.5</v>
@@ -2541,7 +2608,7 @@
         <v>8.5</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>6.1</v>
@@ -2553,16 +2620,16 @@
         <v>20.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.8</v>
+        <v>107</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2595,19 +2662,19 @@
         <v>2</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
         <v>5</v>
@@ -2616,10 +2683,10 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,10 +2695,10 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J13" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
@@ -2693,7 +2760,7 @@
         <v>19.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.356</v>
+        <v>0.352</v>
       </c>
       <c r="O13" t="n">
         <v>16.9</v>
@@ -2714,7 +2781,7 @@
         <v>45.8</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V13" t="n">
         <v>15.2</v>
@@ -2735,13 +2802,13 @@
         <v>21.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2750,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
         <v>16</v>
@@ -2771,13 +2838,13 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>16</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>24</v>
@@ -2947,7 +3014,7 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>10</v>
@@ -2968,16 +3035,16 @@
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -3027,43 +3094,43 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" t="n">
         <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K15" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="N15" t="n">
         <v>0.361</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="Q15" t="n">
         <v>0.6919999999999999</v>
@@ -3075,10 +3142,10 @@
         <v>33</v>
       </c>
       <c r="T15" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U15" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
@@ -3093,22 +3160,22 @@
         <v>5.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA15" t="n">
         <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.7</v>
+        <v>102.4</v>
       </c>
       <c r="AC15" t="n">
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
         <v>17</v>
@@ -3117,13 +3184,13 @@
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
         <v>8</v>
@@ -3135,10 +3202,10 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3159,10 +3226,10 @@
         <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
@@ -3242,31 +3309,31 @@
         <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0.777</v>
       </c>
       <c r="R16" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="S16" t="n">
         <v>29.6</v>
       </c>
       <c r="T16" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U16" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V16" t="n">
         <v>14.6</v>
       </c>
       <c r="W16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>5.2</v>
@@ -3281,16 +3348,16 @@
         <v>19.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
         <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3302,13 +3369,13 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
         <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3323,19 +3390,19 @@
         <v>22</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
         <v>23</v>
@@ -3344,7 +3411,7 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
@@ -3356,13 +3423,13 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -3391,22 +3458,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J17" t="n">
         <v>78.7</v>
@@ -3424,10 +3491,10 @@
         <v>0.387</v>
       </c>
       <c r="O17" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0.764</v>
@@ -3448,7 +3515,7 @@
         <v>13.5</v>
       </c>
       <c r="W17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>5.1</v>
@@ -3457,7 +3524,7 @@
         <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
         <v>20.4</v>
@@ -3478,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
         <v>4</v>
@@ -3502,16 +3569,16 @@
         <v>3</v>
       </c>
       <c r="AO17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP17" t="n">
         <v>13</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>15</v>
       </c>
       <c r="AR17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS17" t="n">
         <v>19</v>
@@ -3520,13 +3587,13 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX17" t="n">
         <v>16</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3681,19 +3748,19 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
         <v>13</v>
@@ -3702,7 +3769,7 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV18" t="n">
         <v>9</v>
@@ -3714,13 +3781,13 @@
         <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -3836,13 +3903,13 @@
         <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
         <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3875,28 +3942,28 @@
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
         <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4082,22 @@
         <v>-3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
@@ -4054,7 +4121,7 @@
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
@@ -4078,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4090,7 +4157,7 @@
         <v>21</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4206,19 +4273,19 @@
         <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>19</v>
       </c>
       <c r="AP21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ21" t="n">
         <v>16</v>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -4301,64 +4368,64 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.742</v>
+        <v>0.738</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J22" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.484</v>
+        <v>0.482</v>
       </c>
       <c r="L22" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M22" t="n">
         <v>19.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="O22" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="P22" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.832</v>
       </c>
       <c r="R22" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S22" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X22" t="n">
         <v>7.6</v>
@@ -4370,16 +4437,16 @@
         <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>107</v>
+        <v>106.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,7 +4461,7 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4427,10 +4494,10 @@
         <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
         <v>18</v>
@@ -4451,7 +4518,7 @@
         <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" t="n">
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>0.27</v>
+        <v>0.274</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J23" t="n">
         <v>83.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="O23" t="n">
         <v>12.4</v>
@@ -4522,28 +4589,28 @@
         <v>16.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R23" t="n">
         <v>10.6</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
         <v>6.1</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
         <v>5</v>
@@ -4552,16 +4619,16 @@
         <v>19.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.4</v>
+        <v>-6.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4600,22 +4667,22 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4633,10 +4700,10 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
       <c r="H24" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I24" t="n">
         <v>37</v>
       </c>
       <c r="J24" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L24" t="n">
         <v>6.2</v>
@@ -4695,16 +4762,16 @@
         <v>17.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O24" t="n">
         <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
@@ -4713,19 +4780,19 @@
         <v>30.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U24" t="n">
         <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W24" t="n">
         <v>7.3</v>
       </c>
       <c r="X24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y24" t="n">
         <v>4.8</v>
@@ -4734,13 +4801,13 @@
         <v>18.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="AB24" t="n">
         <v>92.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="AD24" t="n">
         <v>20</v>
@@ -4749,7 +4816,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="n">
         <v>21</v>
@@ -4758,10 +4825,10 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
@@ -4773,7 +4840,7 @@
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,13 +4852,13 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU24" t="n">
         <v>14</v>
@@ -4803,10 +4870,10 @@
         <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E25" t="n">
         <v>21</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J25" t="n">
         <v>84</v>
       </c>
       <c r="K25" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L25" t="n">
         <v>5.6</v>
       </c>
       <c r="M25" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N25" t="n">
         <v>0.327</v>
       </c>
       <c r="O25" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="P25" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R25" t="n">
         <v>11.5</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T25" t="n">
         <v>41.5</v>
       </c>
       <c r="U25" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="V25" t="n">
         <v>15.2</v>
@@ -4913,28 +4980,28 @@
         <v>5.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA25" t="n">
         <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.5</v>
+        <v>94.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>-5.6</v>
+        <v>-5.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF25" t="n">
         <v>23</v>
       </c>
       <c r="AG25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
         <v>15</v>
@@ -4943,7 +5010,7 @@
         <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
         <v>20</v>
@@ -4970,7 +5037,7 @@
         <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
         <v>20</v>
@@ -4997,7 +5064,7 @@
         <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" t="n">
         <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.445</v>
       </c>
       <c r="L26" t="n">
         <v>8.1</v>
@@ -5059,7 +5126,7 @@
         <v>23.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="O26" t="n">
         <v>16.3</v>
@@ -5068,10 +5135,10 @@
         <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S26" t="n">
         <v>30.4</v>
@@ -5083,28 +5150,28 @@
         <v>21.6</v>
       </c>
       <c r="V26" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>98</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.8</v>
+        <v>-2.3</v>
       </c>
       <c r="AD26" t="n">
         <v>20</v>
@@ -5122,7 +5189,7 @@
         <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
         <v>15</v>
@@ -5137,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
         <v>20</v>
@@ -5155,19 +5222,19 @@
         <v>17</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5179,7 +5246,7 @@
         <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -5211,58 +5278,58 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
         <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>0.344</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J27" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L27" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M27" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O27" t="n">
         <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R27" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S27" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T27" t="n">
         <v>40.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V27" t="n">
         <v>15.1</v>
@@ -5280,16 +5347,16 @@
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.8</v>
+        <v>98.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5298,19 +5365,19 @@
         <v>28</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ27" t="n">
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
@@ -5328,7 +5395,7 @@
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
@@ -5340,13 +5407,13 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
         <v>20</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5355,16 +5422,16 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>14</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
         <v>48</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.762</v>
+        <v>0.774</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="J28" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.489</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0.788</v>
@@ -5438,19 +5505,19 @@
         <v>7.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="V28" t="n">
         <v>14.6</v>
       </c>
       <c r="W28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X28" t="n">
         <v>5.3</v>
@@ -5465,25 +5532,25 @@
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.8</v>
+        <v>104.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP28" t="n">
         <v>17</v>
@@ -5528,13 +5595,13 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" t="n">
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0.381</v>
+        <v>0.387</v>
       </c>
       <c r="H29" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L29" t="n">
         <v>7.4</v>
@@ -5608,25 +5675,25 @@
         <v>0.351</v>
       </c>
       <c r="O29" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P29" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0.782</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U29" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V29" t="n">
         <v>13.3</v>
@@ -5641,19 +5708,19 @@
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="AC29" t="n">
         <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5668,13 +5735,13 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
         <v>11</v>
@@ -5686,25 +5753,25 @@
         <v>21</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT29" t="n">
         <v>29</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5716,16 +5783,16 @@
         <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB29" t="n">
         <v>16</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>15</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
         <v>32</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0.516</v>
+        <v>0.525</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
@@ -5775,7 +5842,7 @@
         <v>37</v>
       </c>
       <c r="J30" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K30" t="n">
         <v>0.451</v>
@@ -5784,31 +5851,31 @@
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="O30" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P30" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R30" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S30" t="n">
         <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U30" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
@@ -5820,40 +5887,40 @@
         <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z30" t="n">
         <v>21.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC30" t="n">
         <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
         <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK30" t="n">
         <v>14</v>
@@ -5862,10 +5929,10 @@
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,22 +5941,22 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>12</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5907,7 +5974,7 @@
         <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>0.317</v>
+        <v>0.322</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
@@ -5957,34 +6024,34 @@
         <v>35.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="O31" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="P31" t="n">
         <v>20</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S31" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T31" t="n">
         <v>43.4</v>
@@ -5993,28 +6060,28 @@
         <v>21.8</v>
       </c>
       <c r="V31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.5</v>
+        <v>91.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AD31" t="n">
         <v>25</v>
@@ -6035,19 +6102,19 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
@@ -6056,31 +6123,31 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV31" t="n">
         <v>29</v>
       </c>
       <c r="AW31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX31" t="n">
         <v>22</v>
       </c>
       <c r="AY31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-8-2012-13</t>
+          <t>2013-03-08</t>
         </is>
       </c>
     </row>
